--- a/route/mini series/s-126(bata mini).xlsx
+++ b/route/mini series/s-126(bata mini).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\testing_gps_wifi_esp8266\mini series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\NEXBUS_LIVE\route\mini series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE03CB56-9382-45CD-B7A4-5E9D4926CD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FF81D2-9811-4E4C-A674-EA4F06C48807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{595B35FD-1FB9-4637-A8C5-8201801681EA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="10920" xr2:uid="{595B35FD-1FB9-4637-A8C5-8201801681EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,9 +74,6 @@
     <t>MOLLIC BAZAR(BATA)(22°30'36.2"N 88°13'24.5"E)</t>
   </si>
   <si>
-    <t>BBD Bagh METRO(Down)(22°34'38.7"N 88°21'08.9"E)</t>
-  </si>
-  <si>
     <t>BOTTALA(BATA)(22°30'24.1"N 88°13'33.6"E)</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>GLAXO LAB(22°31'30.8"N 88°18'20.9"E)</t>
   </si>
   <si>
-    <t>Santoshpur (Down)(22°30'47.6"N 88°16'17.7"E)</t>
-  </si>
-  <si>
     <t>Hide Road More(22°32'16.8"N 88°18'34.2"E)</t>
   </si>
   <si>
@@ -270,6 +264,12 @@
   </si>
   <si>
     <t>Howrah Railway Station(22°35'08.0"N 88°20'38.8"E)</t>
+  </si>
+  <si>
+    <t>BBD Bagh METRO(Down)(22°34'21.3"N 88°21'03.1"E)</t>
+  </si>
+  <si>
+    <t>Santoshpur (Down)(22°30'45.9"N 88°16'07.4"E)</t>
   </si>
 </sst>
 </file>
@@ -676,7 +676,7 @@
   <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="52.5703125" style="4" customWidth="1"/>
     <col min="2" max="2" width="63.42578125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -725,268 +725,268 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B39" s="3"/>
     </row>

--- a/route/mini series/s-126(bata mini).xlsx
+++ b/route/mini series/s-126(bata mini).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\NEXBUS_LIVE\route\mini series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FF81D2-9811-4E4C-A674-EA4F06C48807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245C141-D639-4692-AA33-BF756F4B2811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="10920" xr2:uid="{595B35FD-1FB9-4637-A8C5-8201801681EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{595B35FD-1FB9-4637-A8C5-8201801681EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>Batanagar River Side(22°30'35.5"N 88°13'04.8"E)</t>
   </si>
   <si>
-    <t>Howrah Station(22°35'09.9"N 88°20'38.1"E)</t>
-  </si>
-  <si>
     <t>HILAND GREENS(22°30'45.0"N 88°13'02.9"E)</t>
   </si>
   <si>
@@ -270,6 +267,9 @@
   </si>
   <si>
     <t>Santoshpur (Down)(22°30'45.9"N 88°16'07.4"E)</t>
+  </si>
+  <si>
+    <t>Howrah Station (Down)(22°35'09.9"N 88°20'38.1"E)</t>
   </si>
 </sst>
 </file>
@@ -327,16 +327,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -676,359 +676,358 @@
   <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="63.42578125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="52.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="63.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="3" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="3" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="3" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="3" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="3" t="s">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="3" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="3"/>
-    </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
